--- a/ai-governance-main/backend/Agents/predefined_risks.xlsx
+++ b/ai-governance-main/backend/Agents/predefined_risks.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10824"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jhanakshukla/Desktop/rakfort ai governance/governance-agents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pranay Gupta\Pictures\AI-Goverance-Health\ai-governance-main\backend\Agents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34EB245F-6B3F-044A-A9EA-06741F9F5BDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E0A7B58-7C29-4D20-A3AF-FC43F28B4251}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet" sheetId="1" r:id="rId1"/>
@@ -930,9 +930,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F61"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="72.6640625" customWidth="1"/>
+    <col min="5" max="5" width="103" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="24.33203125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -952,7 +957,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -972,7 +977,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -992,7 +997,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -1012,7 +1017,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -1032,7 +1037,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -1052,7 +1057,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -1072,7 +1077,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>28</v>
       </c>
@@ -1092,7 +1097,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>31</v>
       </c>
@@ -1112,7 +1117,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>34</v>
       </c>
@@ -1132,7 +1137,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>37</v>
       </c>
@@ -1152,7 +1157,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>40</v>
       </c>
@@ -1172,7 +1177,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>43</v>
       </c>
@@ -1192,7 +1197,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>46</v>
       </c>
@@ -1212,7 +1217,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>49</v>
       </c>
@@ -1232,7 +1237,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>52</v>
       </c>
@@ -1252,7 +1257,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>55</v>
       </c>
@@ -1272,7 +1277,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>58</v>
       </c>
@@ -1292,7 +1297,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>61</v>
       </c>
@@ -1312,7 +1317,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>64</v>
       </c>
@@ -1332,7 +1337,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>67</v>
       </c>
@@ -1352,7 +1357,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>70</v>
       </c>
@@ -1372,7 +1377,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>73</v>
       </c>
@@ -1392,7 +1397,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>76</v>
       </c>
@@ -1412,7 +1417,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>79</v>
       </c>
@@ -1432,7 +1437,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>82</v>
       </c>
@@ -1452,7 +1457,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>85</v>
       </c>
@@ -1472,7 +1477,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>88</v>
       </c>
@@ -1492,7 +1497,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>91</v>
       </c>
@@ -1512,7 +1517,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>94</v>
       </c>
@@ -1532,7 +1537,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>97</v>
       </c>
@@ -1552,7 +1557,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>100</v>
       </c>
@@ -1572,7 +1577,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>103</v>
       </c>
@@ -1592,7 +1597,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>106</v>
       </c>
@@ -1612,7 +1617,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>109</v>
       </c>
@@ -1632,7 +1637,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>112</v>
       </c>
@@ -1652,7 +1657,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>115</v>
       </c>
@@ -1672,7 +1677,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>118</v>
       </c>
@@ -1692,7 +1697,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>121</v>
       </c>
@@ -1712,7 +1717,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>124</v>
       </c>
@@ -1732,7 +1737,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>127</v>
       </c>
@@ -1752,7 +1757,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>130</v>
       </c>
@@ -1772,7 +1777,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>133</v>
       </c>
@@ -1792,7 +1797,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>136</v>
       </c>
@@ -1812,7 +1817,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>139</v>
       </c>
@@ -1832,7 +1837,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>142</v>
       </c>
@@ -1852,7 +1857,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>145</v>
       </c>
@@ -1872,7 +1877,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>148</v>
       </c>
@@ -1892,7 +1897,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>151</v>
       </c>
@@ -1912,7 +1917,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>154</v>
       </c>
@@ -1932,7 +1937,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>157</v>
       </c>
@@ -1952,7 +1957,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>160</v>
       </c>
@@ -1972,7 +1977,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>163</v>
       </c>
@@ -1992,7 +1997,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>166</v>
       </c>
@@ -2012,7 +2017,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>169</v>
       </c>
@@ -2032,7 +2037,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>172</v>
       </c>
@@ -2052,7 +2057,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>175</v>
       </c>
@@ -2072,7 +2077,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>178</v>
       </c>
@@ -2092,7 +2097,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>181</v>
       </c>
@@ -2112,7 +2117,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>184</v>
       </c>
@@ -2132,7 +2137,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>187</v>
       </c>
